--- a/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Existing sensitivity label taxonomy has been reviewed for Copilot readiness with gaps documented; Mandatory labeling is enabled for all in-scope M365 workloads; Encryption settings on high-sensitivity labels are confirmed compatible with intended Copilot behavior (block or allow processing); "Copilot Restricted" sublabel (or equivalent) is configured and tested for highest-sensitivity content (Recommended and Regulated levels); Auto-labeling policies are configured for Copilot-generated content (Recommended and Regulated levels); DLP policies integrating sensitivity labels cover Copilot interaction channels (Recommended and Regulated levels); Label coverage meets governance level targets (&gt;50% Baseline / &gt;75% Recommended / &gt;90% Regulated); Label inheritance behavior has been tested across Copilot surfaces (Regulated level); Label taxonomy review cadence is established (annual minimum; quarterly for Regulated); Label governance decisions and configurations are documented and accessible for regulatory examination</t>
+          <t>Sensitivity-label taxonomy document with AI-readiness review date; Labels mapped to Copilot DLP content-exclusion rules; Auto-labeling policy configuration for high-risk content types; Label usage report showing coverage across Copilot-grounded sites</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>DLP policy export showing 'Microsoft 365 Copilot' location in scope; Both policy types present: label-based response blocking AND SIT-based prompt blocking; Policy mode = Enforce (not Test / TestWithNotifications); Match-event report from Purview &gt; Activity Explorer for the last 30 days; Override workflow document showing who can request and approve overrides</t>
+          <t>DLP policy export showing 'Microsoft 365 Copilot and Copilot Chat' location or CopilotExperiences enforcement plane in scope; Three Copilot DLP scenarios present: sensitivity-label content processing, SIT prompt processing, and SIT external web-search restriction; Microsoft 365 admin center Web Content setting evidence showing web search scoped per approved user/group; Policy mode = Enforce (not Test / TestWithNotifications); Match-event report from Microsoft Purview portal &gt; Activity Explorer for the last 30 days; Override workflow document showing who can request and approve overrides</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Label Taxonomy Deployed: Confirm all required labels (Public, Internal, Confidential, Highly Confidential) are published and visible to users in Office applications; Label Groups Migration Status: Verify current taxonomy structure — confirm whether migration from parent labels to label groups has been completed or is scheduled; Default Label Active: Open a new Word document and verify the "Internal — General" label is automatically applied; Label Inheritance: Use Copilot to summarize a Confidential-labeled document and verify the output inherits the "Confidential" label; Highly Confidential Blocking: Attempt to reference a Highly Confidential document in a Copilot prompt — verify Copilot does not process the content and a DLP notification is generated; Agent Label Inheritance: For at least one deployed Copilot Studio agent, verify the effective inherited label matches the highest label across its knowledge sources; Auto-Labeling Accuracy: Review auto-labeling simulation results and confirm &lt;3% false positive rate for deployed SIT-based rules; verify nested conditions function as designed; Downgrade Justification: Attempt to change a label from Confidential to Internal — verify the system requires justification and logs the event; Copilot Pages Label: Create a Copilot Page from content that references a Confidential document — verify the Page inherits the Confidential label; Visual Markings: Open a Confidential-labeled document and confirm headers/footers/watermarks appear as configured; Audit Trail: Verify that label application and modification events appear in the Unified Audit Log; Policy Documentation: Confirm that label taxonomy documentation, label groups migration records, deployment records, and review cadence are maintained and accessible for examination</t>
+          <t>Sensitivity-label taxonomy with Copilot content classification mapping; Auto-labeling policy configuration and coverage report; Label usage report from Activity Explorer for the last 30 days; Evidence of label propagation to Copilot-generated outputs</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>RSS Status: Confirm Restricted SharePoint Search is enabled in the M365 Admin Center; Allow List Accuracy: Verify the RSS allow list contains only sites that have passed data hygiene review; Exclusion Enforcement: Query Copilot Chat for content known to exist on an excluded site — confirm no results are returned from that site; Allow List Enforcement: Query Copilot Chat for content on an allowed site — confirm results are returned normally; Data Access Governance Reports: Confirm monthly reports are generated and reviewed, with remediation actions tracked; Sensitive Site Exclusion: Verify that executive, HR, legal, compliance, and M&amp;A sites are excluded from Copilot grounding; Change Control Process: Confirm a documented change control process exists for RSS allow list modifications; User Communication: Verify that users understand Copilot's data access scope and any limitations imposed by RSS; Permission Hygiene: Run the "Overshared sites" report and confirm that no sites on the RSS allow list appear as overshared; Expansion Tracking: Confirm a documented plan exists for expanding the RSS allow list over time, with milestones and hygiene criteria</t>
+          <t>Grounding scope policy with approved knowledge-source list; Per-agent or per-site scope limits documentation; Review cadence for grounding scope (quarterly or better); Approval records for adding new grounding sources</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>IRM Policy Active: Verify at least one IRM policy is active that includes Copilot activity signals; Risky Agents Policy: Confirm the auto-deployed Risky Agents policy is present and active for Copilot Studio and Azure AI Foundry agents; verify alert routing is configured; AI Usage Indicators: Confirm the AI usage indicator category is enabled and thresholds are set appropriately for the organization's Copilot deployment scale; IRM Triage Agent: Verify the Triage Agent is enabled and producing context summaries for IRM alerts; confirm it is documented in the model inventory; Data Risk Graphs: Confirm data risk graphs are accessible in the investigation workspace and are being used as part of investigation procedures; Signal Collection: Confirm that Copilot interaction data appears in the IRM signal timeline for test users; HR Connector (if applicable): Verify the HR data connector is importing termination/resignation data successfully; Alert Generation: Trigger a test scenario (e.g., high-volume Copilot usage) and confirm an IRM alert is generated; Alert Routing: Verify that IRM alerts are delivered to the designated compliance team within the defined SLA; agent risk alerts route to both compliance and agent deployment owners; Adaptive Protection: Confirm that Adaptive Protection is enabled and that risk level changes result in corresponding DLP enforcement adjustments for Copilot; Custom Indicators: Verify that FSI-specific custom indicators (MNPI probing, client data aggregation, agent data volume) are configured and functional; Investigation Workflow: Confirm documented procedures exist for investigating IRM alerts related to Copilot and agent usage, incorporating Triage Agent recommendations; Privacy Controls: Verify that anonymization is enabled for initial alert triage and that access to IRM investigation data is restricted to authorized investigators; Periodic Review: Confirm that IRM policies are reviewed quarterly with threshold adjustments based on false positive rates and detection effectiveness</t>
+          <t>Insider Risk policy configuration including Copilot indicators; Alert triage cadence and escalation path documentation; Recent alert review log (last 30 days); Integration with HR/legal escalation workflows</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>List all active retention policies in Purview — Policies covering Microsoft Copilot experiences, Exchange, OneDrive, SharePoint, and Teams are present and enabled; Delete a Copilot Chat message and verify recovery — Content is recoverable from the Recoverable Items folder within the retention period; Verify Copilot Pages are covered by retention — Copilot Pages appear in eDiscovery search of OneDrive/Copilot experiences content; Run a retention policy status report — All policies show "On" status with no distribution errors; Verify differentiated retention periods — 3-year policies apply to communications; 6-year policies apply to financial records; Test preservation hold activation — Hold is applied and content is preserved within 4 hours of activation; Verify regulatory record label immutability — Content with regulatory record label cannot be deleted or modified by users; Run cross-workload retention gap analysis — No Copilot content locations fall outside active retention policy scope; Verify departed employee content retention — Inactive mailbox and OneDrive content remain subject to retention policies; Test disposition review workflow — Records reaching end of retention trigger disposition review for authorized reviewers; Verify Microsoft Copilot experiences policy distribution — Copilot experiences retention policy shows DistributionStatus: Success; Confirm threaded summary retention coverage — Teams meeting recaps retained independently of source transcript deletion</t>
+          <t>Retention policy export covering Copilot interaction locations; Retention duration aligned to regulatory minimum (often 7 years for FINRA/SEC); Retention label configuration for Copilot content types; Verification that Copilot Pages/Notebooks are in retention scope</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Run a content search for CopilotInteraction content using the unified search builder — Copilot Chat history appears in search results; Search for Copilot Pages by file type — Copilot Pages (.fluid/.loop) appear in OneDrive search results; Confirm pre-migration cases include Copilot content location — "Microsoft Copilot experiences" data source is present in existing cases; Place a custodian on hold and verify Copilot content is preserved — Deleted Copilot content is recoverable from held locations; Create an eDiscovery case from template — Case with pre-configured custodian groups and saved queries is created within 30 minutes; Export Copilot content in production format — Export file contains valid, readable Copilot interaction records; Apply Copilot surface filter in unified experience — Search results are filterable by surface (e.g., Microsoft 365 Copilot, Teams Copilot); Run a mock FINRA 8210 response drill — Complete case creation, search, review, and export within 8 business hours; Verify cross-workload search coverage — Single search returns Copilot content from Exchange, OneDrive, SharePoint, and Teams; Test custodian hold notification workflow — Automated hold notice is sent and acknowledged within 24 hours; Verify privilege review workflow — Privileged Copilot content is flagged and excluded from production; Document chain-of-custody for exported content — Export log includes hash values, timestamps, and handler identification</t>
+          <t>Test eDiscovery search results confirming Copilot content is discoverable; Custodian hold configuration targeting Copilot data sources; eDiscovery readiness documentation for Copilot; Confirmation that Copilot Pages/Notebooks are in eDiscovery scope</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Send a test message containing promissory language via Outlook Copilot — Message is flagged and appears in reviewer dashboard within 24 hours; Verify policy covers both Exchange and Teams locations — Policy location settings include both workloads; Confirm reviewer access to Communication Compliance dashboard — Assigned reviewers can access and disposition flagged items; Test trainable classifier detection — Classifier correctly flags test messages with regulatory compliance issues; Verify escalation workflow — Unreviewed items past SLA trigger escalation notification; Run monthly false positive analysis — False positive rate is below 30% (tuned threshold); Verify IRM integration is enabled for high-risk CC policies — IRM Settings &gt; Communication Compliance integration shows enabled status; Trigger a CC policy match and verify IRM indicator appears — Within 24 hours of a CC match, a corresponding risk indicator appears in the IRM dashboard for the user; Test pre-send review for high-risk communications — Copilot-drafted messages to high-risk clients are held for supervisory approval; Verify FINRA 3120 testing documentation — Annual testing records demonstrate communication compliance effectiveness; Confirm integration with compliance case management — Flagged items create cases in the firm's compliance system; Review communication compliance trend report — Quarterly report shows detection volumes, review outcomes, and Copilot-specific violation patterns</t>
+          <t>Communication compliance policy configuration covering Copilot channels; Review queue log showing reviews within the last 30 days; Escalation path documentation for policy matches; Coverage confirmation for Teams and Outlook Copilot interactions</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Send a test Copilot-drafted email with promissory language to an external recipient — Message is flagged by Communication Compliance policy; Verify that written supervisory procedures address Copilot-drafted communications — WSPs include specific section on AI-assisted communications; Verify principal pre-approval workflow for retail communications — Test retail communication routed to supervisor before distribution; Test firm-approved prompt library availability — Registered representatives can access approved prompts for common client communication scenarios; Review monthly sampling results — Documented sample of Copilot-drafted client communications with 2210 compliance assessment; Verify trainable classifier detection — Classifier correctly flags Copilot-drafted communications with 2210 violations; Run quarterly FINRA 3120 testing — Testing records demonstrate effectiveness of Copilot communication compliance program; Verify examination-ready documentation — Evidence package demonstrates complete 2210 compliance program for Copilot communications; Test pre-send review workflow end-to-end — Copilot-drafted communication is held, reviewed, approved/rejected, with full audit trail; Verify Copilot-specific violation tracking — Dashboard separately reports Copilot-related vs. human-authored 2210 violations</t>
+          <t>Principal review workflow for Copilot-drafted communications; Detection pattern configuration for prohibited marketing language; FINRA 2210 communication type coverage documentation; Recent review log showing principal approvals</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Review WSPs for Copilot-specific addendum — WSPs include comprehensive Copilot usage procedures including agent scope; Verify supervisor designations — Qualified principals are designated for Copilot supervisory oversight; Confirm pre-approval workflow for retail communications — Test retail communication is held for principal approval; Review sampling documentation — Sampling methodology is documented and sample reviews are recorded; Verify supervisor training completion — All designated Copilot supervisors have completed required training including agent supervision; Test escalation workflow — Flagged Copilot communication is escalated within SLA when reviewer does not act; Review annual testing report — FINRA 3120 testing covers Copilot-specific procedures including agent supervision effectiveness with documented findings; Verify real-time supervisory dashboard — Dashboard shows Copilot usage volumes, review status, and exception alerts; Test examination-ready evidence package — Evidence package demonstrates complete supervisory system for Copilot activities; Verify enhanced supervision procedures — Associated persons with compliance history have documented heightened Copilot supervision</t>
+          <t>Designated supervisory principal for Copilot-related activities; Written Supervisory Procedures (WSPs) addressing Copilot use; Documented review cadence and recent review evidence; Escalation path for supervisory concerns about Copilot outputs</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Review regulatory reporting inventory for Copilot coverage — All applicable reporting obligations include Copilot-specific triggers; Verify incident classification includes Copilot categories — Copilot incident types are defined in the classification framework; Test escalation workflow with simulated Copilot incident — Escalation reaches appropriate level within target timeframes; Verify UDAAP monitoring policies are active — Communication Compliance flags test customer content with UDAAP indicators; Review automated report template completeness — Templates cover all required fields for each regulatory report type; Verify dashboard tracks Copilot-specific complaint trends — Dashboard shows Copilot-related complaint volume, categories, and trends; Test Sarbanes-Oxley §404 control assessment for Copilot processes — Assessment documents Copilot controls with testing results and findings; Verify examination-ready report packages — Pre-populated packages are available for each primary regulator; Conduct tabletop exercise for Copilot regulatory incident — Exercise completed with documented lessons learned and procedure updates; Verify multi-regulator coordination procedures — Reporting matrix shows all applicable regulators with contact information and timelines</t>
+          <t>Regulatory reporting schedule including Copilot-related items; Most recent report or certification referencing Copilot; Evidence trail documentation for Copilot regulatory reports; SOX attestation evidence (if applicable to ICFR)</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Verify Copilot is registered in the model inventory — Model entry exists with complete fields including risk tier, model owner, and proportionality rationale (if applicable); Review use-case documentation — Approved and prohibited uses are documented and communicated; Verify known limitations are documented and communicated — Limitation documentation is available to all Copilot users; Verify proportionality determination is documented — OCC Bulletin 2025-26 cited with usage scope and institution characteristics supporting tier selection; Review quarterly output quality metrics — Metrics are tracked and reported for high-risk use cases; Verify periodic output quality monitoring is implemented — Output monitoring covers accuracy, hallucination rate, and bias indicators; Verify fair lending testing is conducted — Testing methodology and results are documented; Review AI governance committee minutes for Copilot discussion — Copilot MRM is a regular agenda item; Verify annual comprehensive MRM assessment is completed — Assessment follows SR 11-7 / OCC Bulletin 2011-12 structure and documents findings; Review third-party assessment results — Independent assessment validates governance framework effectiveness; Verify examination-ready MRM documentation package — Complete package is assembled and current; Review fair lending statistical testing results — Disparate impact testing shows no statistically significant bias in Copilot-assisted lending activities</t>
+          <t>Model risk management review document for Copilot; Validation methodology and limitation documentation; Ongoing monitoring plan for model performance; Model inventory entry for Copilot (if applicable)</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Review AI disclosure policy — Policy exists, addresses Copilot, and has been distributed to all associated persons; Verify approved terminology guide is published — Guide is accessible and referenced in compliance training; Audit marketing materials for AI claims accuracy — All AI claims are factually accurate and not misleading; Test email footer disclosure deployment — AI disclosure footer appears on client communications from Copilot-licensed users; Verify marketing review process includes AI claims step — Review checklist includes AI-specific review criteria with documented approvals; Test unauthorized AI claims detection — Communication Compliance policy flags test message with prohibited AI terminology; Review quarterly AI marketing claim audit — Audit is completed with documented findings and remediation; Verify state law compliance matrix — Matrix covers all jurisdictions where firm operates with current requirements; Review examination-ready documentation package — Complete AI disclosure and anti-AI-washing documentation is assembled; Verify independent marketing review — Third-party review of AI-related marketing claims is completed and documented</t>
+          <t>AI disclosure template(s) reviewed by legal/compliance; Process documentation for applying disclosure to external content; SEC Marketing Rule alignment documentation; Evidence of disclosure usage in recent external communications</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Verify Copilot is included in Reg S-P risk assessment — Risk assessment documents Copilot NPI access scope and controls; Test DLP policy for NPI in Copilot responses — Copilot-surfaced SSN is blocked; policy tip is displayed to user; Verify privacy notice addresses AI tool usage — Privacy notice discloses use of AI tools in processing customer information; Verify written incident response program exists and covers Copilot — Program includes Copilot-specific scenarios with written notification procedures (Rule 248.30(a)(4)); Verify 72-hour vendor notification procedure is documented — Written procedure identifies Microsoft notification path and 72-hour trigger per Rule 248.30(a)(3)); Test sensitivity label auto-labeling for NPI content — Documents containing NPI patterns are automatically labeled; Test incident response plan covers Copilot NPI scenarios — Plan includes Copilot-specific scenarios with all notification timelines (72-hour vendor, 30-day customer); Test information barrier enforcement in Copilot — Copilot does not surface NPI across barrier boundaries; Run tabletop exercise for Copilot NPI breach — Exercise tests 72-hour vendor notification and 30-day customer notification timelines with documented outcomes; Verify real-time NPI access monitoring — Sentinel alerts trigger for anomalous Copilot NPI access patterns; Review independent safeguard effectiveness assessment — Assessment validates Copilot NPI controls and identifies gaps; Verify examination-ready documentation — Complete Reg S-P compliance package for Copilot, including incident response program documentation and compliance date evidence</t>
+          <t>Privacy impact assessment for Copilot NPI processing; DLP policy configuration preventing NPI surfacing outside authorized workflows; SEC Reg S-P alignment documentation for Copilot; GLBA §501(b) safeguards review covering Copilot</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Verify Copilot record classification matrix exists — Matrix maps all Copilot content types to 17a-3/4 categories, including mobile access paths; Confirm retention policies cover all Copilot content locations — No Copilot content location (including managed mobile) is outside retention policy scope; Test record retrieval for examination response — Copilot records are retrievable and exportable within target timeframes; Verify mobile Copilot requires managed device — Conditional Access or MDM policy restricts Copilot mobile access to managed/compliant devices; Verify differentiated retention periods — 3-year and 6-year retention applied correctly by record category; Verify 17a-4(f) compliance approach is documented — Option A (audit-trail alternative per Rule 17a-4(f)(2)(ii)(A)) or Option B (WORM vendor attestation) is selected and documented; Test retention label regulatory record functionality — Content marked as regulatory record cannot be deleted or modified; attempts are logged; Verify metadata preservation — Exported records include timestamp, author, recipients, and Copilot indicator; Verify WORM storage compliance or audit-trail alternative — Records are stored per the selected 17a-4(f) compliance path with appropriate documentation; Verify Preservation Lock on retention policies — Retention policies cannot be modified or deleted by any administrator; Test chain-of-custody documentation — Complete chain-of-custody log generated for mock examination production; Verify MDM device compliance for mobile Copilot — Intune device compliance + app protection policies enforced; mobile audit log review documented; Run annual 17a-4 compliance assessment — Assessment documents compliance status for all Copilot record categories and the audit-trail alternative (if applicable)</t>
+          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration for Copilot records (if applicable); Retrievability test results for examiner response readiness; Retention duration aligned to SEC 17a-4 / FINRA 4511</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Verify evidence requirements are defined for each control — Evidence matrix exists with complete fields for all Copilot governance controls; Verify quarterly evidence collection schedule — Schedule is documented with assigned responsibilities; Review most recent evidence pack for completeness — Evidence pack contains all required evidence types for all in-scope controls; Test automated evidence collection scripts — Scripts execute successfully and produce valid evidence files; Verify evidence quality review procedures — Quality review checklist is completed and signed for most recent evidence pack; Test evidence integrity controls — Hash verification confirms evidence has not been modified since collection; Verify Sarbanes-Oxley §§302/404 evidence for Copilot controls — Evidence meets PCAOB auditing standard requirements; Verify management attestation is current — Most recent attestation is signed and stored in the evidence pack; Test examination-ready evidence production — Evidence pack for specified regulator is assembled within 2 business days; Verify independent evidence completeness review — Independent review is documented with findings and remediation</t>
+          <t>Evidence-collection runbook document with collector domain coverage; Sample evidence pack from most recent collection run; Audit attestation template aligned to regulatory requirements; Collection schedule and most recent run date</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>

--- a/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Purview Compliance Admin  |  FSI Copilot Governance Framework v1.4  |  17 controls</t>
+          <t>Role: Purview Compliance Admin  |  FSI Copilot Governance Framework v1.8  |  18 controls</t>
         </is>
       </c>
     </row>
@@ -1228,14 +1228,53 @@
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft Scout Governance</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>P4 – Operations &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I21"/>
+  <autoFilter ref="A4:I22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
+    <dataValidation sqref="H5:H22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Purview Compliance Admin  |  FSI Copilot Governance Framework v1.8  |  18 controls</t>
+          <t>Role: Purview Compliance Admin  |  FSI Copilot Governance Framework v1.8.0  |  20 controls</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.8a</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>AI Disclosure, Transparency, and SEC Marketing Rule</t>
+          <t>Generative AI Model Governance for Microsoft 365 Copilot</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Is AI disclosure language presented to customers / counterparties before any Copilot-generated content is shared externally?</t>
+          <t>Has a generative-AI model-governance review (NIST AI RMF 1.0 / ISO/IEC 42001, addressing the SR 26-2 / OCC 2026-13 generative-AI exclusion) been completed for Copilot?</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>AI disclosure template(s) reviewed by legal/compliance; Process documentation for applying disclosure to external content; SEC Marketing Rule alignment documentation; Evidence of disclosure usage in recent external communications</t>
+          <t>Generative-AI governance review document for Copilot; NIST AI RMF 1.0 alignment documentation; Bias testing and safety evaluation results; Responsible-AI principles adoption evidence</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
@@ -1114,12 +1114,12 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>SEC Reg S-P -- Privacy of Consumer Financial Information</t>
+          <t>AI Disclosure, Transparency, and SEC Marketing Rule</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Have SEC Reg S-P / GLBA §501(b) privacy controls been reviewed for Copilot processing of customer NPI?</t>
+          <t>Is AI disclosure language presented to customers / counterparties before any Copilot-generated content is shared externally?</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Privacy impact assessment for Copilot NPI processing; DLP policy configuration preventing NPI surfacing outside authorized workflows; SEC Reg S-P alignment documentation for Copilot; GLBA §501(b) safeguards review covering Copilot</t>
+          <t>AI disclosure template(s) reviewed by legal/compliance; Process documentation for applying disclosure to external content; SEC Marketing Rule alignment documentation; Evidence of disclosure usage in recent external communications</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
@@ -1153,12 +1153,12 @@
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Record Keeping and Books-and-Records Compliance (SEC 17a-3/4, FINRA 4511)</t>
+          <t>SEC Reg S-P -- Privacy of Consumer Financial Information</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Are Copilot interactions captured into the firm's books-and-records system per SEC Rule 17a-4 (where applicable)?</t>
+          <t>Have SEC Reg S-P / GLBA §501(b) privacy controls been reviewed for Copilot processing of customer NPI?</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration for Copilot records (if applicable); Retrievability test results for examiner response readiness; Retention duration aligned to SEC 17a-4 / FINRA 4511</t>
+          <t>Privacy impact assessment for Copilot NPI processing; DLP policy configuration preventing NPI surfacing outside authorized workflows; SEC Reg S-P alignment documentation for Copilot; GLBA §501(b) safeguards review covering Copilot</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
@@ -1192,12 +1192,12 @@
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Evidence Collection and Audit Attestation</t>
+          <t>Record Keeping and Books-and-Records Compliance (SEC 17a-3/4, FINRA 4511)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Is there a documented evidence-collection runbook used for Copilot-related audits and exam responses?</t>
+          <t>Are Copilot interactions captured into the firm's books-and-records system per SEC Rule 17a-4 (where applicable)?</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Evidence-collection runbook document with collector domain coverage; Sample evidence pack from most recent collection run; Audit attestation template aligned to regulatory requirements; Collection schedule and most recent run date</t>
+          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration for Copilot records (if applicable); Retrievability test results for examiner response readiness; Retention duration aligned to SEC 17a-4 / FINRA 4511</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
@@ -1231,17 +1231,17 @@
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Microsoft Scout Governance</t>
+          <t>Evidence Collection and Audit Attestation</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>P4 – Operations &amp; Lifecycle</t>
+          <t>P3 – Compliance &amp; Records</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1251,30 +1251,108 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+          <t>Purview audit/eDiscovery/retention; FINRA/SEC records</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+          <t>Is there a documented evidence-collection runbook used for Copilot-related audits and exam responses?</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+          <t>Evidence-collection runbook document with collector domain coverage; Sample evidence pack from most recent collection run; Audit attestation template aligned to regulatory requirements; Collection schedule and most recent run date</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Copilot Pages and Notebooks Retention and Provenance</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>P3 – Compliance &amp; Records</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Purview audit/eDiscovery/retention; FINRA/SEC records</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Are branch-aware Copilot Pages, Notebook section-level coverage, and Loop component provenance addressed in retention and records-management policies?</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Retention policy covering Copilot Pages and Notebooks; Branch-aware retention configuration documentation; Provenance metadata strategy for Copilot-generated content; Section-level retention granularity documentation</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft Scout Governance</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>P4 – Operations &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I22"/>
+  <autoFilter ref="A4:I24"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
+    <dataValidation sqref="H5:H24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Purview Compliance Admin  |  FSI Copilot Governance Framework v1.4  |  17 controls</t>
+          <t>Role: Purview Compliance Admin  |  FSI Copilot Governance Framework v1.8.0  |  20 controls</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.8a</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>AI Disclosure, Transparency, and SEC Marketing Rule</t>
+          <t>Generative AI Model Governance for Microsoft 365 Copilot</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Is AI disclosure language presented to customers / counterparties before any Copilot-generated content is shared externally?</t>
+          <t>Has a generative-AI model-governance review (NIST AI RMF 1.0 / ISO/IEC 42001, addressing the SR 26-2 / OCC 2026-13 generative-AI exclusion) been completed for Copilot?</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>AI disclosure template(s) reviewed by legal/compliance; Process documentation for applying disclosure to external content; SEC Marketing Rule alignment documentation; Evidence of disclosure usage in recent external communications</t>
+          <t>Generative-AI governance review document for Copilot; NIST AI RMF 1.0 alignment documentation; Bias testing and safety evaluation results; Responsible-AI principles adoption evidence</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
@@ -1114,12 +1114,12 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>SEC Reg S-P -- Privacy of Consumer Financial Information</t>
+          <t>AI Disclosure, Transparency, and SEC Marketing Rule</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Have SEC Reg S-P / GLBA §501(b) privacy controls been reviewed for Copilot processing of customer NPI?</t>
+          <t>Is AI disclosure language presented to customers / counterparties before any Copilot-generated content is shared externally?</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Privacy impact assessment for Copilot NPI processing; DLP policy configuration preventing NPI surfacing outside authorized workflows; SEC Reg S-P alignment documentation for Copilot; GLBA §501(b) safeguards review covering Copilot</t>
+          <t>AI disclosure template(s) reviewed by legal/compliance; Process documentation for applying disclosure to external content; SEC Marketing Rule alignment documentation; Evidence of disclosure usage in recent external communications</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
@@ -1153,12 +1153,12 @@
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Record Keeping and Books-and-Records Compliance (SEC 17a-3/4, FINRA 4511)</t>
+          <t>SEC Reg S-P -- Privacy of Consumer Financial Information</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Are Copilot interactions captured into the firm's books-and-records system per SEC Rule 17a-4 (where applicable)?</t>
+          <t>Have SEC Reg S-P / GLBA §501(b) privacy controls been reviewed for Copilot processing of customer NPI?</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration for Copilot records (if applicable); Retrievability test results for examiner response readiness; Retention duration aligned to SEC 17a-4 / FINRA 4511</t>
+          <t>Privacy impact assessment for Copilot NPI processing; DLP policy configuration preventing NPI surfacing outside authorized workflows; SEC Reg S-P alignment documentation for Copilot; GLBA §501(b) safeguards review covering Copilot</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
@@ -1192,12 +1192,12 @@
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Evidence Collection and Audit Attestation</t>
+          <t>Record Keeping and Books-and-Records Compliance (SEC 17a-3/4, FINRA 4511)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1217,25 +1217,142 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Is there a documented evidence-collection runbook used for Copilot-related audits and exam responses?</t>
+          <t>Are Copilot interactions captured into the firm's books-and-records system per SEC Rule 17a-4 (where applicable)?</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Evidence-collection runbook document with collector domain coverage; Sample evidence pack from most recent collection run; Audit attestation template aligned to regulatory requirements; Collection schedule and most recent run date</t>
+          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration for Copilot records (if applicable); Retrievability test results for examiner response readiness; Retention duration aligned to SEC 17a-4 / FINRA 4511</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Evidence Collection and Audit Attestation</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>P3 – Compliance &amp; Records</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Purview audit/eDiscovery/retention; FINRA/SEC records</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Is there a documented evidence-collection runbook used for Copilot-related audits and exam responses?</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Evidence-collection runbook document with collector domain coverage; Sample evidence pack from most recent collection run; Audit attestation template aligned to regulatory requirements; Collection schedule and most recent run date</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Copilot Pages and Notebooks Retention and Provenance</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>P3 – Compliance &amp; Records</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Purview audit/eDiscovery/retention; FINRA/SEC records</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Are branch-aware Copilot Pages, Notebook section-level coverage, and Loop component provenance addressed in retention and records-management policies?</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Retention policy covering Copilot Pages and Notebooks; Branch-aware retention configuration documentation; Provenance metadata strategy for Copilot-generated content; Section-level retention granularity documentation</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft Scout Governance</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>P4 – Operations &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I21"/>
+  <autoFilter ref="A4:I24"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
+    <dataValidation sqref="H5:H24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration for Copilot records (if applicable); Retrievability test results for examiner response readiness; Retention duration aligned to SEC 17a-4 / FINRA 4511</t>
+          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration or audit-trail alternative documentation per Rule 17a-4(f)(2) (SEC Release No. 34-96034, 87 FR 66412 (Nov. 3, 2022)) for Copilot records; Retrievability test results for examiner response readiness; Retention duration aligned to Rule 17a-4(f)(2) / FINRA 4511</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>

--- a/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration or audit-trail alternative documentation per Rule 17a-4(f)(2) (SEC Release No. 34-96034, 87 FR 66412 (Nov. 3, 2022)) for Copilot records; Retrievability test results for examiner response readiness; Retention duration aligned to Rule 17a-4(f)(2) / FINRA 4511</t>
+          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration or audit-trail alternative documentation per Rule 17a-4(f)(2) (SEC Release No. 34-96034, 87 FR 66412 (Nov. 3, 2022)) for Copilot records; Retrievability test results for examiner response readiness; Retention duration aligned to SEC Rule 17a-4 / FINRA 4511</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>

--- a/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration for Copilot records (if applicable); Retrievability test results for examiner response readiness; Retention duration aligned to SEC 17a-4 / FINRA 4511</t>
+          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration or audit-trail alternative documentation per Rule 17a-4(f)(2) (SEC Release No. 34-96034, 87 FR 66412 (Nov. 3, 2022)) for Copilot records; Retrievability test results for examiner response readiness; Retention duration aligned to SEC Rule 17a-4 / FINRA 4511</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>

--- a/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>DLP Policies for Microsoft 365 Copilot Interactions</t>
+          <t>Are DLP policies for Copilot interactions configured, tested, and reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Sensitivity Labels and Copilot Content Classification</t>
+          <t>Are sensitivity labels applied to Copilot-grounded content and label coverage reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>eDiscovery for Copilot-Generated Content</t>
+          <t>Are eDiscovery cases and holds configured to capture Copilot interaction content when legally required?</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">

--- a/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>DLP policy export showing 'Microsoft 365 Copilot and Copilot Chat' location or CopilotExperiences enforcement plane in scope; Three Copilot DLP scenarios present: sensitivity-label content processing, SIT prompt processing, and SIT external web-search restriction; Microsoft 365 admin center Web Content setting evidence showing web search scoped per approved user/group; Policy mode = Enforce (not Test / TestWithNotifications); Match-event report from Microsoft Purview portal &gt; Activity Explorer for the last 30 days; Override workflow document showing who can request and approve overrides</t>
+          <t>DLP policy export showing the 'Microsoft 365 Copilot and Copilot Chat' location and CopilotExperiences enforcement plane in scope; Applicable Copilot DLP scenarios present: sensitivity-label content processing, SIT prompt processing where available, SIT external web-search restriction, and assessment of preview external-email exclusion; Cloud Policy service evidence for Allow web search in Copilot showing the approved user/group scope; Policy mode and rollout evidence showing applicable rules are enforced after simulation; Match-event report from Microsoft Purview portal &gt; Solutions &gt; DSPM &gt; Discover &gt; Activity explorer for the last 30 days; Direct-upload file-content limitation test and compensating source-control evidence; Exception workflow showing who can request and approve policy-scope changes</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Privacy impact assessment for Copilot NPI processing; DLP policy configuration preventing NPI surfacing outside authorized workflows; SEC Reg S-P alignment documentation for Copilot; GLBA §501(b) safeguards review covering Copilot</t>
+          <t>Privacy impact assessment for Copilot NPI processing; Custom DLP policy configuration showing the Copilot location, applicable supported actions, mode, scope, and alerts; Synthetic tests for label exclusion, typed-prompt blocking where available, web-search restriction, external-email exclusion where available, and the direct-upload limitation; Purview Audit CopilotInteraction evidence and DSPM AI activity review; Copilot Pages and Notebooks SharePoint Embedded limitation review and admin-policy disposition; SEC Reg S-P alignment documentation for Copilot; GLBA §501(b) safeguards review covering Copilot</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
